--- a/src/tool/地点坐标.xlsx
+++ b/src/tool/地点坐标.xlsx
@@ -1689,6 +1689,11 @@
   <sheetPr/>
   <dimension ref="A1:C164"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="2"/>
+  <cols>
+    <col min="1" max="1" width="37" customWidth="1"/>
+    <col min="2" max="2" width="14.2222222222222" customWidth="1"/>
+    <col min="3" max="3" width="21.5555555555556" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
